--- a/tabelas/PR_PREMIO.xlsx
+++ b/tabelas/PR_PREMIO.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3f4ef99f068508f/STANG/5.MotorCalculo/MotorTransporteV2/tabelas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99477d7318b1e097/14. Gisele^0Jardel/Atuá Estratégia ^0 Análises/8. Projetos/STANG/5.MotorCalculo/01_RC_Ambiental/MotorTransporteV5/tabelas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="8_{6B52802C-5F77-4A94-B0AB-84BCD71D6197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08692BA9-D4A1-4272-BBA1-9FC4291B9D34}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{6B52802C-5F77-4A94-B0AB-84BCD71D6197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D61E9BD-A584-428D-B07D-B875330645A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77FAD20C-44E5-4827-8893-D4E5A201625A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77FAD20C-44E5-4827-8893-D4E5A201625A}"/>
   </bookViews>
   <sheets>
     <sheet name="PR_PREMIO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PR_PREMIO!$C$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PR_PREMIO!$C$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -509,20 +509,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B6CFE4-61AD-40DD-B0AE-A336CB719A94}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="4" customWidth="1"/>
-    <col min="4" max="8" width="8.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="4" customWidth="1"/>
-    <col min="10" max="13" width="8.7109375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="3"/>
+    <col min="1" max="2" width="14.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="4" customWidth="1"/>
+    <col min="4" max="8" width="8.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="4" customWidth="1"/>
+    <col min="10" max="13" width="8.6640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -569,12 +569,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>3029.69</v>
+        <v>2726.721</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -595,26 +595,32 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>6522.5</v>
+        <v>1043.6000000000001</v>
       </c>
       <c r="J2" s="2">
-        <v>6818.75</v>
+        <v>1091</v>
       </c>
       <c r="K2" s="2">
-        <v>6794.14</v>
+        <v>1087.0624</v>
       </c>
       <c r="L2" s="2">
-        <v>6993.76</v>
+        <v>1119.0016000000001</v>
       </c>
       <c r="M2" s="2">
-        <v>8888.01</v>
+        <v>1422.0816000000002</v>
       </c>
       <c r="N2" s="7">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="O2" s="7">
         <v>1</v>
       </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
